--- a/src/main/resources/python/MultifacetedModeling/DataOutput/GPR/frequency.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/DataOutput/GPR/frequency.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,187 +660,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.43243243243243246</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.40540540540540543</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4594594594594595</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.6486486486486487</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4594594594594595</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.5135135135135135</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>0.5405405405405406</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4594594594594595</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.7567567567567568</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5405405405405406</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.5405405405405406</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3783783783783784</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>0.5675675675675675</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5675675675675675</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.6486486486486487</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.40540540540540543</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.43243243243243246</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.6756756756756757</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3783783783783784</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.40540540540540543</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.4864864864864865</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3783783783783784</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2972972972972973</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>0.5135135135135135</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.35135135135135137</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.40540540540540543</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>0.7027027027027027</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>0.5135135135135135</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.40540540540540543</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3783783783783784</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2702702702702703</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.2702702702702703</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.6486486486486487</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.16216216216216217</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.40540540540540543</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.5675675675675675</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2702702702702703</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -850,194 +850,194 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.3783783783783784</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>0.4594594594594595</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5135135135135135</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.4864864864864865</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.5945945945945946</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.6216216216216216</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.5675675675675675</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.42105263157894735</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.5789473684210527</t>
+          <t>0.6111111111111112</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5263157894736842</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.631578947368421</t>
+          <t>0.6666666666666666</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.5263157894736842</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.5263157894736842</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.631578947368421</t>
+          <t>0.6666666666666666</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.5263157894736842</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.631578947368421</t>
+          <t>0.6666666666666666</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.47368421052631576</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.47368421052631576</t>
+          <t>0.4444444444444444</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.5789473684210527</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.47368421052631576</t>
+          <t>0.4444444444444444</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.2631578947368421</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.47368421052631576</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.5789473684210527</t>
+          <t>0.5555555555555556</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.5263157894736842</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.21052631578947367</t>
+          <t>0.2222222222222222</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.631578947368421</t>
+          <t>0.6111111111111112</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.47368421052631576</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.2631578947368421</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.2631578947368421</t>
+          <t>0.2222222222222222</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.3157894736842105</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.42105263157894735</t>
+          <t>0.4444444444444444</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1047,27 +1047,27 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.2631578947368421</t>
+          <t>0.2222222222222222</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.2631578947368421</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.2631578947368421</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.47368421052631576</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1077,224 +1077,224 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.3157894736842105</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.15789473684210525</t>
+          <t>0.1111111111111111</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.47368421052631576</t>
+          <t>0.4444444444444444</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.15789473684210525</t>
+          <t>0.1111111111111111</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.3684210526315789</t>
+          <t>0.3888888888888889</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0.5217391304347826</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.5217391304347826</t>
+          <t>0.5416666666666666</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5217391304347826</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6521739130434783</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5217391304347826</t>
+          <t>0.4583333333333333</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6086956521739131</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7391304347826086</t>
+          <t>0.8333333333333334</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5217391304347826</t>
+          <t>0.5416666666666666</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.8695652173913043</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.43478260869565216</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.4782608695652174</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.391304347826087</t>
+          <t>0.2916666666666667</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.8260869565217391</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.4782608695652174</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5217391304347826</t>
+          <t>0.5833333333333334</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.21739130434782608</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4782608695652174</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.43478260869565216</t>
+          <t>0.4583333333333333</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.30434782608695654</t>
+          <t>0.4166666666666667</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.34782608695652173</t>
+          <t>0.4583333333333333</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.2608695652173913</t>
+          <t>0.20833333333333334</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.4782608695652174</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.2608695652173913</t>
+          <t>0.2916666666666667</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.4782608695652174</t>
+          <t>0.5833333333333334</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.4782608695652174</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.43478260869565216</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.5217391304347826</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.4782608695652174</t>
+          <t>0.5416666666666666</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.34782608695652173</t>
+          <t>0.20833333333333334</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.2608695652173913</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.21739130434782608</t>
+          <t>0.3333333333333333</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.5652173913043478</t>
+          <t>0.16666666666666666</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.21739130434782608</t>
+          <t>0.4166666666666667</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.043478260869565216</t>
+          <t>0.16666666666666666</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5652173913043478</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.2608695652173913</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.08695652173913043</t>
+          <t>0.20833333333333334</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1304,264 +1304,264 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.2608695652173913</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.43478260869565216</t>
+          <t>0.5416666666666666</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.34782608695652173</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.43478260869565216</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.5652173913043478</t>
+          <t>0.4166666666666667</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.43478260869565216</t>
+          <t>0.2916666666666667</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6086956521739131</t>
+          <t>0.5416666666666666</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.5714285714285714</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.5714285714285714</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.7619047619047619</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.8571428571428571</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.42857142857142855</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.42857142857142855</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.8095238095238095</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.19047619047619047</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.42857142857142855</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.2857142857142857</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.38095238095238093</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.19047619047619047</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.23809523809523808</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.42857142857142855</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.38095238095238093</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.2857142857142857</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.23809523809523808</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.5714285714285714</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.14285714285714285</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.5238095238095238</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.23809523809523808</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.09523809523809523</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.19047619047619047</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.47619047619047616</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>0.3333333333333333</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.5555555555555556</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.4444444444444444</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.3888888888888889</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.9444444444444444</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.6111111111111112</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.3333333333333333</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.2777777777777778</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.5555555555555556</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.3888888888888889</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.6666666666666666</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.5555555555555556</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.3888888888888889</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0.4444444444444444</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.4444444444444444</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.4444444444444444</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.2222222222222222</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.2777777777777778</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.2222222222222222</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.5555555555555556</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.3888888888888889</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.6111111111111112</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.3333333333333333</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.6111111111111112</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.05555555555555555</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0.3333333333333333</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>0.3888888888888889</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.16666666666666666</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0.3888888888888889</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.2222222222222222</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0.3333333333333333</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.2222222222222222</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0.1111111111111111</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>0.5555555555555556</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0.3333333333333333</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.3888888888888889</t>
+          <t>0.42857142857142855</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4444444444444444</t>
+          <t>0.5714285714285714</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.2777777777777778</t>
+          <t>0.42857142857142855</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5555555555555556</t>
+          <t>0.6190476190476191</t>
         </is>
       </c>
     </row>
